--- a/resources/indicator_schema_data_household_template.xlsx
+++ b/resources/indicator_schema_data_household_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\iphRa\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636C18E2-FFCE-49A8-B283-B4051172F11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8247CD-D655-49FC-BEB6-5F377CD3B9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22710" yWindow="3450" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4305" yWindow="4620" windowWidth="14250" windowHeight="15405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>indicator_name</t>
   </si>
@@ -322,6 +322,18 @@
   </si>
   <si>
     <t>sanitation_facility_cat_col=@variable_map$wash_sanitation_facility_cat,sanitation_facility_improved_val=c(@value_map$wash_sanitation_facility_cat$improved),sanitation_facility_unimproved_val=c(@value_map$wash_sanitation_facility_cat$unimproved),sanitation_facility_open_defecation_val=c(@value_map$wash_sanitation_facility_cat$surface_water),shared_sanitation_col=@variable_map$wash_sanitation_facility_shared_cat,shared_sanitation_yes_val=c(@value_map$wash_sanitation_facility_shared_cat$shared),shared_sanitation_no_val=c(@value_map$wash_sanitation_facility_shared_cat$not_shared),</t>
+  </si>
+  <si>
+    <t>interview_time_indicator</t>
+  </si>
+  <si>
+    <t>add_interview_time</t>
+  </si>
+  <si>
+    <t>start,end</t>
+  </si>
+  <si>
+    <t>start_col=@variable_map$start,end_col=@variable_map$end</t>
   </si>
 </sst>
 </file>
@@ -366,12 +378,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -675,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -708,327 +721,341 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+        <v>102</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>85</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>86</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>47</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>49</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="15" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>52</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>60</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>61</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>69</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>66</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>75</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>76</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>81</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>92</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F21" t="s">
         <v>77</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D17" r:id="rId1" display="sanitation_facility_cat_col=@variable_map$wash_sanitation_facility_cat,sanitation_facility_improved_val=c(@value_map$wash_sanitation_facility_cat$improved),sanitation_facility_unimproved_val=c(@value_map$wash_sanitation_facility_cat$unimproved),sanitation_facility_open_defecation_val=c(@value_map$wash_sanitation_facility_cat$surface_water),shared_sanitation_col=@variable_map$wash_sanitation_facility_shared_cat,shared_sanitation_yes_val=c(@value_map$wash_sanitation_facility_shared_cat$shared),shared_sanitation_no_val=c(@value_map$wash_sanitation_facility_shared_cat$not_shared)," xr:uid="{13837254-8BF6-463A-A8D1-78570DF6B7DD}"/>
+    <hyperlink ref="D18" r:id="rId1" display="sanitation_facility_cat_col=@variable_map$wash_sanitation_facility_cat,sanitation_facility_improved_val=c(@value_map$wash_sanitation_facility_cat$improved),sanitation_facility_unimproved_val=c(@value_map$wash_sanitation_facility_cat$unimproved),sanitation_facility_open_defecation_val=c(@value_map$wash_sanitation_facility_cat$surface_water),shared_sanitation_col=@variable_map$wash_sanitation_facility_shared_cat,shared_sanitation_yes_val=c(@value_map$wash_sanitation_facility_shared_cat$shared),shared_sanitation_no_val=c(@value_map$wash_sanitation_facility_shared_cat$not_shared)," xr:uid="{13837254-8BF6-463A-A8D1-78570DF6B7DD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
